--- a/experiment_stimuli/Block6.xlsx
+++ b/experiment_stimuli/Block6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\sdt\experiment_stimuli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\lab\sdtWhole\experiment_stimuli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10B4620-977C-4EEB-B8F3-85197747BB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4BA939-D4B5-4732-B037-34A0D2BCB3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2562" yWindow="1896" windowWidth="17172" windowHeight="11064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67935" yWindow="3330" windowWidth="17280" windowHeight="8910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>The sharp rod was a lance.</t>
   </si>
   <si>
-    <t>His gait was a mild limp.</t>
-  </si>
-  <si>
     <t>The parade was a military march.</t>
   </si>
   <si>
@@ -95,6 +92,9 @@
   </si>
   <si>
     <t>The funny sound was his snore.</t>
+  </si>
+  <si>
+    <t>His walk was a mild limp.</t>
   </si>
 </sst>
 </file>
@@ -380,7 +380,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -425,7 +425,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
@@ -493,7 +493,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>6</v>
@@ -510,7 +510,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>6</v>
@@ -524,10 +524,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -541,10 +541,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -558,10 +558,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -575,10 +575,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
@@ -592,10 +592,10 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>6</v>
@@ -609,10 +609,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>6</v>
@@ -626,10 +626,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>6</v>
@@ -643,10 +643,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>6</v>
